--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.77922</v>
+        <v>16.84238</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49547</v>
+        <v>16.67654</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82867</v>
+        <v>16.82985</v>
       </c>
       <c r="F2" t="n">
-        <v>41.85337</v>
+        <v>41.95831</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05128</v>
+        <v>0.05034</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7979</v>
+        <v>1.83876</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.79436</v>
+        <v>16.67175</v>
       </c>
       <c r="D3" t="n">
-        <v>16.22479</v>
+        <v>16.50383</v>
       </c>
       <c r="E3" t="n">
-        <v>16.43037</v>
+        <v>16.64494</v>
       </c>
       <c r="F3" t="n">
-        <v>42.82063</v>
+        <v>42.36664</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05246</v>
+        <v>0.05001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80101</v>
+        <v>1.80941</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.53872</v>
+        <v>16.96573</v>
       </c>
       <c r="D4" t="n">
-        <v>16.40287</v>
+        <v>16.44837</v>
       </c>
       <c r="E4" t="n">
-        <v>16.70211</v>
+        <v>16.58882</v>
       </c>
       <c r="F4" t="n">
-        <v>42.73574</v>
+        <v>42.96446</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05013</v>
+        <v>0.04951</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8107</v>
+        <v>1.82577</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.74843</v>
+        <v>16.76498</v>
       </c>
       <c r="D6" t="n">
-        <v>15.65962</v>
+        <v>16.01925</v>
       </c>
       <c r="E6" t="n">
-        <v>16.59746</v>
+        <v>16.43218</v>
       </c>
       <c r="F6" t="n">
-        <v>21.84552</v>
+        <v>21.42747</v>
       </c>
       <c r="G6" t="n">
-        <v>34.94773</v>
+        <v>34.14302</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.7072</v>
+        <v>16.67917</v>
       </c>
       <c r="D7" t="n">
-        <v>15.75871</v>
+        <v>15.93077</v>
       </c>
       <c r="E7" t="n">
-        <v>16.06395</v>
+        <v>16.40696</v>
       </c>
       <c r="F7" t="n">
-        <v>21.68179</v>
+        <v>21.73451</v>
       </c>
       <c r="G7" t="n">
-        <v>33.84628</v>
+        <v>34.75573</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.68572</v>
+        <v>16.67206</v>
       </c>
       <c r="D8" t="n">
-        <v>15.78456</v>
+        <v>15.49486</v>
       </c>
       <c r="E8" t="n">
-        <v>16.36773</v>
+        <v>16.55756</v>
       </c>
       <c r="F8" t="n">
-        <v>22.01886</v>
+        <v>21.27968</v>
       </c>
       <c r="G8" t="n">
-        <v>33.25623</v>
+        <v>34.38332</v>
       </c>
     </row>
   </sheetData>
